--- a/public/reports/DLF_NS_Financial_Model.xlsx
+++ b/public/reports/DLF_NS_Financial_Model.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="601">
   <si>
     <t>DLF Limited (DLF.NS)</t>
   </si>
@@ -57,7 +57,7 @@
     <t>WITHHELD</t>
   </si>
   <si>
-    <t>Upside / (downside)</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited)</t>
   </si>
   <si>
     <t>n/a</t>
@@ -201,19 +201,19 @@
     <t>Snapshot ID</t>
   </si>
   <si>
-    <t>snap_DLF_NS_75470c63bef6</t>
+    <t>snap_DLF_NS_b844a0b66419</t>
   </si>
   <si>
     <t>Snapshot SHA-256</t>
   </si>
   <si>
-    <t>75470c63bef69cc76ccdbffd0d6f6d3ca3ed6cd319ef3625d69f5707fea9cfda</t>
+    <t>b844a0b66419deb01694e6f298f621dd835c37c5430e8cd35bd6fbb1ef67b0c1</t>
   </si>
   <si>
     <t>Built at</t>
   </si>
   <si>
-    <t>2026-11-01T14:58:05.476Z</t>
+    <t>2026-11-01T15:04:41.411Z</t>
   </si>
   <si>
     <t>Analysis status</t>
@@ -279,7 +279,7 @@
     <t>Fair value per share</t>
   </si>
   <si>
-    <t>Upside / (downside) %</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited) %</t>
   </si>
   <si>
     <t>v1 formula-trace coverage % (a different measure from "figures that reconcile" in the run-status table)</t>
@@ -819,7 +819,7 @@
     <t>Withheld: Linked three-statement forecast -- the reported FY26 balance sheet does not balance as opened (assets 73465 vs liabilities + equity 47499 Cr); no forecast is built on it</t>
   </si>
   <si>
-    <t>Withheld: DCF cross-check -- Not eligible by methodology: valuation methodology routes this archetype (REAL_ESTATE) to Sum of the parts and prohibits the consolidated FCFF DCF. It is not forced to populate a sheet, and no DCF stance is published.</t>
+    <t>Withheld: DCF cross-check -- Not eligible by methodology: valuation methodology routes this archetype (REAL_ESTATE) to Sum of the parts and prohibits the consolidated FCFF DCF. It is not forced to populate a sheet, and no DCF reading is published.</t>
   </si>
   <si>
     <t>Withheld: Reverse DCF -- a reverse DCF inverts a consolidated FCFF DCF, which this archetype's methodology prohibits</t>
@@ -1026,7 +1026,7 @@
     <t>Forensic audit complete: Overall Health: UNAVAILABLE | Altman Z: N/A (N/A) | Piotroski F: N/A/9 | Beneish M: N/A (N/A).</t>
   </si>
   <si>
-    <t>ACCOUNTING QUALITY (verdict CAUTION)</t>
+    <t>ACCOUNTING QUALITY (assessment CAUTION)</t>
   </si>
   <si>
     <t>Check</t>
@@ -1578,40 +1578,16 @@
     <t>Assumptions hash (12)</t>
   </si>
   <si>
-    <t>snap_DLF_NS_75470c63bef6  &lt;- THIS WORKBOOK</t>
+    <t>snap_DLF_NS_b844a0b66419  &lt;- THIS WORKBOOK</t>
   </si>
   <si>
     <t>74234e98afe7</t>
   </si>
   <si>
-    <t>snap_DLF_NS_c860ef844639</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:58:05.430Z</t>
-  </si>
-  <si>
-    <t>snap_DLF_NS_712fe6dd5791</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:56:07.265Z</t>
-  </si>
-  <si>
-    <t>snap_DLF_NS_155738e6f41c</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:56:07.214Z</t>
-  </si>
-  <si>
-    <t>snap_DLF_NS_6b6c46fb7d4b</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:52:51.070Z</t>
-  </si>
-  <si>
-    <t>snap_DLF_NS_d2d5b387d075</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:52:51.016Z</t>
+    <t>snap_DLF_NS_fe75977cdfb5</t>
+  </si>
+  <si>
+    <t>2026-11-01T15:04:41.361Z</t>
   </si>
   <si>
     <t>OVERRIDES APPLIED TO THIS WORKBOOK</t>
@@ -1722,7 +1698,7 @@
     <t>Difference</t>
   </si>
   <si>
-    <t>No DCF stance without a DCF</t>
+    <t>No DCF reading without a DCF</t>
   </si>
   <si>
     <t>VALUATION</t>
@@ -1731,7 +1707,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>no DCF ran and no stance is published</t>
+    <t>no DCF ran and no reading is published</t>
   </si>
   <si>
     <t>No bonus / split is classified as economic dilution</t>
@@ -1812,7 +1788,7 @@
     <t>DCF cross-check</t>
   </si>
   <si>
-    <t>Not eligible by methodology: valuation methodology routes this archetype (REAL_ESTATE) to Sum of the parts and prohibits the consolidated FCFF DCF. It is not forced to populate a sheet, and no DCF stance is published.</t>
+    <t>Not eligible by methodology: valuation methodology routes this archetype (REAL_ESTATE) to Sum of the parts and prohibits the consolidated FCFF DCF. It is not forced to populate a sheet, and no DCF reading is published.</t>
   </si>
   <si>
     <t>Reverse DCF</t>
@@ -1851,7 +1827,7 @@
     <t>SAVED RECORD AND VERIFIER RECEIPTS</t>
   </si>
   <si>
-    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_DLF_NS_75470c63bef6/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
+    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_DLF_NS_b844a0b66419/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
   </si>
   <si>
     <t>Chart data (editable)</t>
@@ -8588,7 +8564,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
@@ -8707,189 +8683,73 @@
         <v>514</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>518</v>
       </c>
-      <c r="C8" s="14">
-        <v>691.55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>520</v>
       </c>
-      <c r="C9" s="14">
-        <v>691.55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B13" t="s">
         <v>521</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
         <v>522</v>
       </c>
-      <c r="C10" s="14">
-        <v>691.55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>520</v>
+      </c>
+      <c r="B14" t="s">
         <v>523</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C14" t="s">
         <v>524</v>
       </c>
-      <c r="C11" s="14">
-        <v>691.55</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>520</v>
+      </c>
+      <c r="B15" t="s">
         <v>525</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C15" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>528</v>
-      </c>
-      <c r="B17" t="s">
-        <v>529</v>
-      </c>
-      <c r="C17" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>528</v>
-      </c>
-      <c r="B18" t="s">
-        <v>531</v>
-      </c>
-      <c r="C18" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>528</v>
-      </c>
-      <c r="B19" t="s">
-        <v>533</v>
-      </c>
-      <c r="C19" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -8914,17 +8774,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -8936,7 +8796,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>409</v>
@@ -8948,27 +8808,27 @@
         <v>187</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>502</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="B6" t="s">
         <v>417</v>
@@ -8977,13 +8837,13 @@
         <v>5695</v>
       </c>
       <c r="D6" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E6" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F6" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G6" t="s">
         <v>86</v>
@@ -8995,12 +8855,12 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B7" t="s">
         <v>417</v>
@@ -9009,13 +8869,13 @@
         <v>2034</v>
       </c>
       <c r="D7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E7" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F7" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G7" t="s">
         <v>86</v>
@@ -9032,7 +8892,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="B8" t="s">
         <v>453</v>
@@ -9041,13 +8901,13 @@
         <v>6427</v>
       </c>
       <c r="D8" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E8" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F8" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G8" t="s">
         <v>86</v>
@@ -9059,12 +8919,12 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B9" t="s">
         <v>453</v>
@@ -9073,13 +8933,13 @@
         <v>2724</v>
       </c>
       <c r="D9" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E9" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F9" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G9" t="s">
         <v>86</v>
@@ -9096,7 +8956,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B10" t="s">
         <v>467</v>
@@ -9105,13 +8965,13 @@
         <v>7994</v>
       </c>
       <c r="D10" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E10" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F10" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G10" t="s">
         <v>86</v>
@@ -9123,12 +8983,12 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="B11" t="s">
         <v>467</v>
@@ -9137,13 +8997,13 @@
         <v>4367</v>
       </c>
       <c r="D11" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E11" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F11" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G11" t="s">
         <v>86</v>
@@ -9160,7 +9020,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="B12" t="s">
         <v>481</v>
@@ -9169,13 +9029,13 @@
         <v>8194</v>
       </c>
       <c r="D12" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E12" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F12" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G12" t="s">
         <v>86</v>
@@ -9187,12 +9047,12 @@
         <v>7</v>
       </c>
       <c r="J12" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B13" t="s">
         <v>481</v>
@@ -9201,13 +9061,13 @@
         <v>4415</v>
       </c>
       <c r="D13" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E13" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F13" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G13" t="s">
         <v>86</v>
@@ -9224,7 +9084,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -9239,19 +9099,19 @@
         <v>330</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>195</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>334</v>
@@ -9259,13 +9119,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B17" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C17" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -9277,18 +9137,18 @@
         <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="B18" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C18" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -9300,18 +9160,18 @@
         <v>7</v>
       </c>
       <c r="G18" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B19" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C19" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -9323,12 +9183,12 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -9340,41 +9200,41 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B23" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C23" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D23" t="s">
         <v>201</v>
       </c>
       <c r="E23" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -9386,10 +9246,10 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B26" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -9418,10 +9278,10 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="B30" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -9434,97 +9294,97 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B32" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B33" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C33" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B34" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C34" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B35" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="C35" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B36" t="s">
+        <v>586</v>
+      </c>
+      <c r="C36" t="s">
         <v>587</v>
-      </c>
-      <c r="B36" t="s">
-        <v>594</v>
-      </c>
-      <c r="C36" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B37" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C37" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B38" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="C38" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B39" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B40" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -9536,7 +9396,7 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -9556,17 +9416,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9576,7 +9436,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
